--- a/excel_templates/记录表.xlsx
+++ b/excel_templates/记录表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L292"/>
+  <dimension ref="A1:L298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,7 +533,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13800138003.0</t>
+          <t>13800138003</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1329,7 +1329,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1441,7 +1441,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1811,7 +1811,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1923,7 +1923,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2267,7 +2267,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2379,7 +2379,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2433,7 +2433,7 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2487,7 +2487,7 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>15827247200.0</t>
+          <t>15827247200</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>15827247200.0</t>
+          <t>15827247200</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>15827247200.0</t>
+          <t>15827247200</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>15827247200.0</t>
+          <t>15827247200</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>15827247200.0</t>
+          <t>15827247200</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>15827247200.0</t>
+          <t>15827247200</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14218,7 +14218,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14632,7 +14632,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -14872,7 +14872,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -15278,7 +15278,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -15856,7 +15856,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -16204,7 +16204,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -17018,6 +17018,331 @@
         </is>
       </c>
       <c r="L292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2b0c5ed6-ef86-4bbc-942a-fa7a2d1663c2</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>PHO001</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>强制归还</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:12:00</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>管理员强制归还</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>e2a7c9f1-7c31-4191-b56a-9338a79bcc69</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>强制归还</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:13:04</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>管理员强制归还</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2ff89c2f-768b-4199-a57a-50de1fb98efb</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>5244a94d-e4f7-468b-8d9e-0036d86a9dc9</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>找回</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:46:34</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>找回：lan——&gt;保管人自用</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>13800138001</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>设备已找回，保管人自用</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>90dd0d47-a851-4a25-b682-7ed92068b21d</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>qwqe5</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>仪表-005</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>仪表</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>强制归还</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:48:28</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>管理员强制归还</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>a4b6b5c0-b937-41fb-bb2c-9277a9879c04</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>车机</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>转借</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:59:06</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>被转借：test——&gt;lan</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>13800138001</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>用户转借给自己</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ea081e2f-7b64-4917-9399-0963f3980ccd</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>仪表</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>转借</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:22:34</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>lan——&gt;test</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>13986903203</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>用户转借</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel_templates/记录表.xlsx
+++ b/excel_templates/记录表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L298"/>
+  <dimension ref="A1:L299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17344,6 +17344,64 @@
       </c>
       <c r="L298" t="inlineStr"/>
     </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>1ae9cbee-6dd3-4e82-988c-6633c6a7fe0a</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>转借</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:28:53</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>保管人——&gt;test</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>13986903203</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>保管人转借</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel_templates/记录表.xlsx
+++ b/excel_templates/记录表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L299"/>
+  <dimension ref="A1:L313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17402,6 +17402,807 @@
       </c>
       <c r="L299" t="inlineStr"/>
     </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>525f3af0-0e16-4dfa-ab05-fef164fe8378</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>车机</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>强制归还</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:23:34</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>管理员强制归还</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>237ea9d7-4651-4614-85e6-f45ec2bf1098</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>TEG-199</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>iPhone 14 Pro</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>转借</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:24:48</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>lan——&gt;test</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>13986903203</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>用户转借</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>3981fbef-4dec-4c9c-a342-4f06a7ba50bb</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>仪表</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>转借</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:30:08</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>test——&gt;lan</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>13800138001</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>用户转借</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1fb06e6d-54e4-4c81-ae72-fe9faf01fcb2</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>仪表</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>转借</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:33:17</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>被转借：lan——&gt;test</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>13986903203</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>用户转借给自己</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>7e4f0eb8-6daf-4181-a5e6-6f2c71fcefae</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>仪表</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>转借</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:06:10</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>被转借：test——&gt;lan</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>13800138001</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>用户转借给自己</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>f5e9e7b7-4562-4dbf-9813-65d7858fc7e6</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>仪表</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>转借</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:16:01</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>lan——&gt;test</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>13986903203</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>用户转借</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>de6cdb44-2c24-4b6c-977c-bfc89dcd8f38</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>归还</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:16:50</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>13986903203</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>正常归还 - 设备完好，无异常</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>207d0ecf-579f-438f-97d1-abe7754a0a49</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>归还</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:16:51</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>13986903203</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>正常归还 - 设备完好，无异常</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>1ca03486-c58b-4b0e-8f31-13ee20455068</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>保管人变更</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:20:32</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>转让保管人：lan——&gt;test</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>13986903203</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>设备转让保管人</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ca54e561-40ce-4d9d-94a5-30001569d4a9</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>仪表</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>转借</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:20:59</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>被转借：test——&gt;lan</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>13800138001</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>用户转借给自己</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>5af3c86e-171d-45f9-9d16-dfcd3642c5e8</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>仪表</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>转借</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:27:11</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>被转借：lan——&gt;test</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>13986903203</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>用户转借给自己</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>7e975e2c-f54f-42f4-9428-1b5767083608</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>仪表</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>借用人未找到</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:27:58</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>未找到：test——&gt;lan</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>13800138001</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>设备未找到，退回给上一个借用人</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>535570f1-1291-456e-ad96-cd10a7eefbf5</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>借出</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:37:18</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>13800138001</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>测试 - 用于功能测试</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2cfb0d7a-8f37-43a9-b47d-74a62ca1312d</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>归还</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:38:03</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>保管人代还：lan</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>保管人代还设备</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
